--- a/WorkBot/refactor/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>68048</t>
+          <t>71748</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Red Bull - Pink Berry</t>
+          <t>Liquid Death - Squeezed to Death (19.2oz)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,51 +461,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>31.95</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>71748</t>
+          <t>70610</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liquid Death - Squeezed to Death (19.2oz)</t>
+          <t>Vita Coco - Pineapple</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>87.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>70610</t>
+          <t>70630</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vita Coco - Pineapple</t>
+          <t>Vita Coco - Coconut Water 1L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -515,29 +515,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>70630</t>
+          <t>70632</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 1L</t>
+          <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,19 +547,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>106.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>68310</t>
+          <t>71745</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Red Bull - Yellow</t>
+          <t>Liquid Death - Green Guillotine (19.20z)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,120 +569,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>68266</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Red Bull - Watermelon Red</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>68150</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Red Bull - Sugar Free</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>68177</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Red Bull - Amber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>68297</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Red Bull - Blue</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>42.85</t>
+          <t>21.57</t>
         </is>
       </c>
     </row>
